--- a/diseases/d127/2015-2019.xlsx
+++ b/diseases/d127/2015-2019.xlsx
@@ -3492,28 +3492,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -3580,17 +3594,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3615,93 +3629,179 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2016-02-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3833,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3814,42 +3914,42 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3981,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3911,12 +4011,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-02-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3936,68 +4036,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4138,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4059,12 +4173,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4073,39 +4187,125 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4207,12 +4407,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4355,12 +4555,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4380,28 +4580,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4468,17 +4682,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4503,12 +4717,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2016-05-01</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4517,79 +4731,165 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4621,12 +4921,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4651,12 +4951,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2016-05-01</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4702,42 +5002,42 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4769,12 +5069,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4799,12 +5099,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4824,68 +5124,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4912,7 +5226,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4947,12 +5261,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4961,39 +5275,125 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5095,12 +5495,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2016-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5243,12 +5643,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2016-05-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5268,28 +5668,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5356,17 +5770,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5391,12 +5805,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2016-08-01</t>
+          <t>2016-05-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5405,79 +5819,165 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>1</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5509,12 +6009,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5539,12 +6039,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2016-08-01</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5590,42 +6090,42 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5657,12 +6157,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5687,12 +6187,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5712,68 +6212,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5800,7 +6314,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5835,12 +6349,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5849,39 +6363,125 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5983,12 +6583,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6131,12 +6731,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6156,28 +6756,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6244,17 +6858,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6279,12 +6893,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6293,79 +6907,165 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6397,12 +7097,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6427,12 +7127,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6478,42 +7178,42 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6545,12 +7245,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6575,12 +7275,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6600,68 +7300,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6688,7 +7402,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6723,12 +7437,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6737,39 +7451,125 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6871,12 +7671,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6989,12 +7789,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7019,12 +7819,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7046,12 +7846,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7071,7 +7871,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -7084,42 +7884,42 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7951,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7181,12 +7981,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7197,22 +7997,22 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Viral Haemorrhagic Fever</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -7222,12 +8022,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -7237,7 +8037,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7257,12 +8057,12 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>non_additive</t>
+          <t>reported_aggregate</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -7272,12 +8072,12 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -7305,7 +8105,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -7318,42 +8118,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7385,12 +8185,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7415,12 +8215,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7466,42 +8266,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7533,12 +8333,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7563,12 +8363,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7588,68 +8388,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7676,17 +8490,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7711,12 +8525,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7725,79 +8539,165 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7859,12 +8759,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2017-04</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7977,12 +8877,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8007,12 +8907,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8032,68 +8932,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8120,17 +9034,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8155,12 +9069,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2017-06-01</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8169,79 +9083,165 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>1</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8303,12 +9303,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8421,12 +9421,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8451,12 +9451,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2017-08-01</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8476,68 +9476,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8564,17 +9578,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8599,12 +9613,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8613,79 +9627,165 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8747,12 +9847,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8865,12 +9965,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8895,12 +9995,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2017-11-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8920,68 +10020,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9008,17 +10122,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9043,12 +10157,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9057,79 +10171,165 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9161,12 +10361,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9191,12 +10391,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9216,68 +10416,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9304,17 +10518,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9339,12 +10553,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9353,26 +10567,98 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SER_NZ_VHF_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>New Zealand broad viral haemorrhagic fever source category; not equivalent to hantavirus haemorrhagic fever with renal syndrome.</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -9391,7 +10677,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_NZ_VHF_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -9404,42 +10690,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9466,17 +10752,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9501,12 +10787,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9515,165 +10801,79 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>1</v>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9735,12 +10935,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9883,12 +11083,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2018-03-01</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2017-04</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -10031,12 +11231,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2018-04-01</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10179,12 +11379,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2018-05-01</t>
+          <t>2017-06-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10327,12 +11527,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10475,12 +11675,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2017-08-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10623,12 +11823,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10771,12 +11971,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10919,12 +12119,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -11067,12 +12267,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11215,12 +12415,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11333,12 +12533,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11363,12 +12563,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11388,68 +12588,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11476,7 +12690,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -11511,12 +12725,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11525,26 +12739,98 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -11638,17 +12924,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11673,12 +12959,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11687,165 +12973,79 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN73" t="b">
-        <v>1</v>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11907,12 +13107,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12055,12 +13255,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2018-04-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -12203,12 +13403,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2018-05-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12351,12 +13551,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12499,12 +13699,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12647,12 +13847,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12795,12 +13995,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12943,12 +14143,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -13091,12 +14291,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -13239,12 +14439,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -13387,12 +14587,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13472,6 +14672,2030 @@
         </is>
       </c>
       <c r="BC84" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -13603,7 +16827,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -13623,7 +16847,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -13633,7 +16857,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d127/2015-2019.xlsx
+++ b/diseases/d127/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3082,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -10009,9 +10003,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -12577,9 +12568,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -14747,9 +14735,6 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
